--- a/PickAndPlace_驱动板.xlsx
+++ b/PickAndPlace_驱动板.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_07_14" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_DRV8701E_PCB_2026_" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="218">
   <si>
     <t>Designator</t>
   </si>
@@ -61,634 +61,610 @@
     <t>C1</t>
   </si>
   <si>
-    <t>220uF35V8x12KM</t>
-  </si>
-  <si>
-    <t>CAP-TH_BD8.0-P3.50-D0.5-FD</t>
-  </si>
-  <si>
-    <t>11.557mm</t>
-  </si>
-  <si>
-    <t>-4.699mm</t>
-  </si>
-  <si>
-    <t>-6.449mm</t>
+    <t>CGA0805X5R106K350MT</t>
+  </si>
+  <si>
+    <t>C0805</t>
+  </si>
+  <si>
+    <t>23.749mm</t>
+  </si>
+  <si>
+    <t>7.112mm</t>
+  </si>
+  <si>
+    <t>22.749mm</t>
   </si>
   <si>
     <t>T</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R9BB104</t>
+  </si>
+  <si>
+    <t>C0603</t>
+  </si>
+  <si>
+    <t>23.876mm</t>
+  </si>
+  <si>
+    <t>9.144mm</t>
+  </si>
+  <si>
+    <t>23.176mm</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>CL10A105KB8NNNC</t>
+  </si>
+  <si>
+    <t>26.67mm</t>
+  </si>
+  <si>
+    <t>8.255mm</t>
+  </si>
+  <si>
+    <t>8.955mm</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>28.448mm</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>30.226mm</t>
+  </si>
+  <si>
+    <t>7.555mm</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>42.672mm</t>
+  </si>
+  <si>
+    <t>11.684mm</t>
+  </si>
+  <si>
+    <t>43.672mm</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>42.164mm</t>
+  </si>
+  <si>
+    <t>9.779mm</t>
+  </si>
+  <si>
+    <t>42.864mm</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>39.243mm</t>
+  </si>
+  <si>
+    <t>11.049mm</t>
+  </si>
+  <si>
+    <t>11.749mm</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>37.465mm</t>
+  </si>
+  <si>
+    <t>10.349mm</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>35.687mm</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>29.972mm</t>
+  </si>
+  <si>
+    <t>14.351mm</t>
+  </si>
+  <si>
+    <t>13.651mm</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>32.893mm</t>
+  </si>
+  <si>
+    <t>9.652mm</t>
+  </si>
+  <si>
+    <t>32.193mm</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>46.99mm</t>
+  </si>
+  <si>
+    <t>20.828mm</t>
+  </si>
+  <si>
+    <t>47.69mm</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>1N5819HW-7-F</t>
+  </si>
+  <si>
+    <t>SOD-123_L2.7-W1.6-LS3.7-RD</t>
+  </si>
+  <si>
+    <t>23.495mm</t>
+  </si>
+  <si>
+    <t>4.953mm</t>
+  </si>
+  <si>
+    <t>25.13mm</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>42.418mm</t>
+  </si>
+  <si>
+    <t>13.716mm</t>
+  </si>
+  <si>
+    <t>40.783mm</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>NCD0805R1</t>
+  </si>
+  <si>
+    <t>LED0805-R-RD</t>
+  </si>
+  <si>
+    <t>14.224mm</t>
+  </si>
+  <si>
+    <t>1.905mm</t>
+  </si>
+  <si>
+    <t>15.274mm</t>
+  </si>
+  <si>
+    <t>LED2</t>
+  </si>
+  <si>
+    <t>33.147mm</t>
+  </si>
+  <si>
+    <t>1.877mm</t>
+  </si>
+  <si>
+    <t>32.097mm</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>KF301-5.0-2P</t>
+  </si>
+  <si>
+    <t>CONN-TH_P5.00_KF301-5.0-2P</t>
+  </si>
+  <si>
+    <t>3.81mm</t>
+  </si>
+  <si>
+    <t>13.625mm</t>
+  </si>
+  <si>
+    <t>16.125mm</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>220uF/35V</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>CL21B105KBFNNNE</t>
-  </si>
-  <si>
-    <t>C0805</t>
-  </si>
-  <si>
-    <t>41.783mm</t>
-  </si>
-  <si>
-    <t>-9.271mm</t>
-  </si>
-  <si>
-    <t>42.783mm</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>GRM21BR61H106KE43L</t>
-  </si>
-  <si>
-    <t>23.876mm</t>
-  </si>
-  <si>
-    <t>-20.447mm</t>
-  </si>
-  <si>
-    <t>24.876mm</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>CC0603KRX7R9BB104</t>
-  </si>
-  <si>
-    <t>C0603</t>
-  </si>
-  <si>
-    <t>24.13mm</t>
-  </si>
-  <si>
-    <t>-18.542mm</t>
-  </si>
-  <si>
-    <t>24.83mm</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>CL10A105KB8NNNC</t>
-  </si>
-  <si>
-    <t>26.924mm</t>
-  </si>
-  <si>
-    <t>-22.987mm</t>
-  </si>
-  <si>
-    <t>-22.287mm</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>29.083mm</t>
-  </si>
-  <si>
-    <t>-22.225mm</t>
-  </si>
-  <si>
-    <t>-21.525mm</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>31.242mm</t>
-  </si>
-  <si>
-    <t>-22.925mm</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>35.052mm</t>
-  </si>
-  <si>
-    <t>-13.081mm</t>
-  </si>
-  <si>
-    <t>34.052mm</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>34.925mm</t>
-  </si>
-  <si>
-    <t>-20.955mm</t>
-  </si>
-  <si>
-    <t>33.925mm</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>-18.034mm</t>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>62.23mm</t>
+  </si>
+  <si>
+    <t>12.954mm</t>
+  </si>
+  <si>
+    <t>10.454mm</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>28.321mm</t>
+  </si>
+  <si>
+    <t>30.821mm</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>PH2.54-01-03PZS</t>
+  </si>
+  <si>
+    <t>HDR-TH_6P-P2.54-V-M-R2-C3-S2.54</t>
+  </si>
+  <si>
+    <t>40.894mm</t>
+  </si>
+  <si>
+    <t>24.257mm</t>
+  </si>
+  <si>
+    <t>38.354mm</t>
+  </si>
+  <si>
+    <t>22.987mm</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>TPH1R403NL_C83440</t>
+  </si>
+  <si>
+    <t>DSOP-8_L5.0-W5.0-P1.27-LS6.0-BL-EP</t>
+  </si>
+  <si>
+    <t>17.688mm</t>
+  </si>
+  <si>
+    <t>9.28mm</t>
+  </si>
+  <si>
+    <t>14.918mm</t>
+  </si>
+  <si>
+    <t>11.186mm</t>
+  </si>
+  <si>
+    <t>TPH1R403NL</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>17.736mm</t>
+  </si>
+  <si>
+    <t>15.63mm</t>
+  </si>
+  <si>
+    <t>14.966mm</t>
+  </si>
+  <si>
+    <t>17.536mm</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>10.957mm</t>
+  </si>
+  <si>
+    <t>9.218mm</t>
+  </si>
+  <si>
+    <t>9.051mm</t>
+  </si>
+  <si>
+    <t>6.448mm</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>11.005mm</t>
+  </si>
+  <si>
+    <t>16.584mm</t>
+  </si>
+  <si>
+    <t>12.91mm</t>
+  </si>
+  <si>
+    <t>19.354mm</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>48.768mm</t>
+  </si>
+  <si>
+    <t>13.843mm</t>
+  </si>
+  <si>
+    <t>51.538mm</t>
+  </si>
+  <si>
+    <t>11.937mm</t>
+  </si>
+  <si>
+    <t>Q6</t>
+  </si>
+  <si>
+    <t>48.647mm</t>
+  </si>
+  <si>
+    <t>8.137mm</t>
+  </si>
+  <si>
+    <t>51.416mm</t>
+  </si>
+  <si>
+    <t>6.232mm</t>
+  </si>
+  <si>
+    <t>Q7</t>
+  </si>
+  <si>
+    <t>54.949mm</t>
+  </si>
+  <si>
+    <t>14.552mm</t>
+  </si>
+  <si>
+    <t>53.043mm</t>
+  </si>
+  <si>
+    <t>11.782mm</t>
+  </si>
+  <si>
+    <t>Q8</t>
+  </si>
+  <si>
+    <t>54.997mm</t>
+  </si>
+  <si>
+    <t>7.313mm</t>
+  </si>
+  <si>
+    <t>56.902mm</t>
+  </si>
+  <si>
+    <t>10.083mm</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>FRC0603J103 TS</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>35.37mm</t>
+  </si>
+  <si>
+    <t>18.857mm</t>
+  </si>
+  <si>
+    <t>36.124mm</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>35.306mm</t>
+  </si>
+  <si>
+    <t>17.272mm</t>
+  </si>
+  <si>
+    <t>36.059mm</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>47.117mm</t>
+  </si>
+  <si>
+    <t>17.399mm</t>
+  </si>
+  <si>
+    <t>47.87mm</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>19.05mm</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>RC0805FR-072K2L</t>
+  </si>
+  <si>
+    <t>R0805</t>
+  </si>
+  <si>
+    <t>7.62mm</t>
+  </si>
+  <si>
+    <t>32.147mm</t>
+  </si>
+  <si>
+    <t>2.2kΩ</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>33.194mm</t>
+  </si>
+  <si>
+    <t>5.293mm</t>
+  </si>
+  <si>
+    <t>32.194mm</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>SS12D10G4 071</t>
+  </si>
+  <si>
+    <t>SW-TH_SHOU-HAN_SS12D10G4</t>
+  </si>
+  <si>
+    <t>57.023mm</t>
+  </si>
+  <si>
+    <t>52.223mm</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>DRV8701ERGER</t>
+  </si>
+  <si>
+    <t>VQFN-24_L4.0-W4.0-P0.50-BL-EP2.5</t>
+  </si>
+  <si>
+    <t>25.527mm</t>
+  </si>
+  <si>
+    <t>14.859mm</t>
+  </si>
+  <si>
+    <t>24.277mm</t>
+  </si>
+  <si>
+    <t>12.917mm</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>39.242mm</t>
+  </si>
+  <si>
+    <t>5.915mm</t>
+  </si>
+  <si>
+    <t>40.492mm</t>
+  </si>
+  <si>
+    <t>7.857mm</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>SN74HC125PWR</t>
+  </si>
+  <si>
+    <t>TSSOP-14_L5.0-W4.4-P0.65-LS6.5-BL</t>
+  </si>
+  <si>
+    <t>17.78mm</t>
+  </si>
+  <si>
+    <t>37.969mm</t>
+  </si>
+  <si>
+    <t>19.73mm</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>LR8341A-T33</t>
+  </si>
+  <si>
+    <t>SOT-23-3L_L2.9-W1.6-P1.90-LS2.8-BL</t>
+  </si>
+  <si>
+    <t>32.766mm</t>
+  </si>
+  <si>
+    <t>31.816mm</t>
+  </si>
+  <si>
+    <t>12.578mm</t>
   </si>
   <si>
     <t>C11</t>
   </si>
   <si>
-    <t>41.148mm</t>
-  </si>
-  <si>
-    <t>-19.939mm</t>
-  </si>
-  <si>
-    <t>41.848mm</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>36.957mm</t>
-  </si>
-  <si>
-    <t>-17.399mm</t>
-  </si>
-  <si>
-    <t>-18.099mm</t>
-  </si>
-  <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>34.671mm</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>32.385mm</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>1N5819HW_C41431974</t>
-  </si>
-  <si>
-    <t>SOD-123_L2.7-W1.6-LS3.8-RD</t>
-  </si>
-  <si>
-    <t>25.908mm</t>
-  </si>
-  <si>
-    <t>-26.035mm</t>
-  </si>
-  <si>
-    <t>24.173mm</t>
-  </si>
-  <si>
-    <t>1N5819HW</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>40.767mm</t>
-  </si>
-  <si>
-    <t>-16.002mm</t>
-  </si>
-  <si>
-    <t>39.032mm</t>
-  </si>
-  <si>
-    <t>LED1</t>
-  </si>
-  <si>
-    <t>KT-0805G</t>
-  </si>
-  <si>
-    <t>LED0805-R-RD</t>
-  </si>
-  <si>
-    <t>20.447mm</t>
-  </si>
-  <si>
-    <t>-26.416mm</t>
-  </si>
-  <si>
-    <t>21.497mm</t>
-  </si>
-  <si>
-    <t>LED2</t>
-  </si>
-  <si>
-    <t>KT-0805Y</t>
-  </si>
-  <si>
-    <t>49.276mm</t>
-  </si>
-  <si>
-    <t>-25.527mm</t>
-  </si>
-  <si>
-    <t>48.226mm</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>KF301-2P接线端子</t>
-  </si>
-  <si>
-    <t>CONN-TH_XY301V-A-5.0-2P</t>
-  </si>
-  <si>
-    <t>22.479mm</t>
-  </si>
-  <si>
-    <t>-5.334mm</t>
-  </si>
-  <si>
-    <t>24.979mm</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>4.445mm</t>
-  </si>
-  <si>
-    <t>-13.208mm</t>
-  </si>
-  <si>
-    <t>-15.708mm</t>
-  </si>
-  <si>
-    <t>电机1接口</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>60.706mm</t>
-  </si>
-  <si>
-    <t>-14.605mm</t>
-  </si>
-  <si>
-    <t>-12.105mm</t>
-  </si>
-  <si>
-    <t>电机2接口</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>SH-GH1.25-6PWB</t>
-  </si>
-  <si>
-    <t>SW-SMD_SH-GH1.25-6PWB</t>
-  </si>
-  <si>
-    <t>34.29mm</t>
-  </si>
-  <si>
-    <t>-2.921mm</t>
-  </si>
-  <si>
-    <t>31.165mm</t>
-  </si>
-  <si>
-    <t>-1.346mm</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>TPH1R403NL_C83440</t>
-  </si>
-  <si>
-    <t>DSOP-8_L5.0-W5.0-P1.27-LS6.0-BL-EP</t>
-  </si>
-  <si>
-    <t>18.034mm</t>
-  </si>
-  <si>
-    <t>-21.59mm</t>
-  </si>
-  <si>
-    <t>15.264mm</t>
-  </si>
-  <si>
-    <t>-19.684mm</t>
-  </si>
-  <si>
-    <t>TPH1R403NL</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>-15.367mm</t>
-  </si>
-  <si>
-    <t>-13.461mm</t>
-  </si>
-  <si>
-    <t>Q3</t>
-  </si>
-  <si>
-    <t>11.549mm</t>
-  </si>
-  <si>
-    <t>-23.021mm</t>
-  </si>
-  <si>
-    <t>9.644mm</t>
-  </si>
-  <si>
-    <t>-25.791mm</t>
-  </si>
-  <si>
-    <t>Q4</t>
-  </si>
-  <si>
-    <t>11.429mm</t>
-  </si>
-  <si>
-    <t>-13.242mm</t>
-  </si>
-  <si>
-    <t>13.335mm</t>
-  </si>
-  <si>
-    <t>-10.473mm</t>
-  </si>
-  <si>
-    <t>Q5</t>
-  </si>
-  <si>
-    <t>47.49mm</t>
-  </si>
-  <si>
-    <t>-16.165mm</t>
-  </si>
-  <si>
-    <t>50.26mm</t>
-  </si>
-  <si>
-    <t>-18.07mm</t>
-  </si>
-  <si>
-    <t>Q6</t>
-  </si>
-  <si>
-    <t>52.046mm</t>
-  </si>
-  <si>
-    <t>-23.496mm</t>
-  </si>
-  <si>
-    <t>Q7</t>
-  </si>
-  <si>
-    <t>53.332mm</t>
-  </si>
-  <si>
-    <t>-11.344mm</t>
-  </si>
-  <si>
-    <t>55.238mm</t>
-  </si>
-  <si>
-    <t>-8.575mm</t>
-  </si>
-  <si>
-    <t>Q8</t>
-  </si>
-  <si>
-    <t>55.88mm</t>
-  </si>
-  <si>
-    <t>-23.876mm</t>
-  </si>
-  <si>
-    <t>53.974mm</t>
-  </si>
-  <si>
-    <t>-26.646mm</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>0805W8F2201T5E</t>
-  </si>
-  <si>
-    <t>R0805</t>
-  </si>
-  <si>
-    <t>29.845mm</t>
-  </si>
-  <si>
-    <t>-11.176mm</t>
-  </si>
-  <si>
-    <t>28.845mm</t>
-  </si>
-  <si>
-    <t>10K</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>41.91mm</t>
-  </si>
-  <si>
-    <t>-11.43mm</t>
-  </si>
-  <si>
-    <t>42.91mm</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>29.972mm</t>
-  </si>
-  <si>
-    <t>-13.843mm</t>
-  </si>
-  <si>
-    <t>28.972mm</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>42.037mm</t>
-  </si>
-  <si>
-    <t>-13.716mm</t>
-  </si>
-  <si>
-    <t>41.037mm</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>34.964mm</t>
-  </si>
-  <si>
-    <t>-24.042mm</t>
-  </si>
-  <si>
-    <t>33.964mm</t>
-  </si>
-  <si>
-    <t>2.2K</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>34.958mm</t>
-  </si>
-  <si>
-    <t>-26.328mm</t>
-  </si>
-  <si>
-    <t>35.958mm</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>SK-12F04-G050</t>
-  </si>
-  <si>
-    <t>SW-TH_G-SWITCH_SK-12F04-G050</t>
-  </si>
-  <si>
-    <t>48.514mm</t>
-  </si>
-  <si>
-    <t>-4.953mm</t>
-  </si>
-  <si>
-    <t>45.514mm</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>SN74HC125PWR</t>
-  </si>
-  <si>
-    <t>TSSOP-14_L5.0-W4.4-P0.65-LS6.5-BL</t>
-  </si>
-  <si>
-    <t>35.56mm</t>
-  </si>
-  <si>
-    <t>-8.89mm</t>
-  </si>
-  <si>
-    <t>32.635mm</t>
-  </si>
-  <si>
-    <t>-6.94mm</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>DRV8701ERGER</t>
-  </si>
-  <si>
-    <t>VQFN-24_L4.0-W4.0-P0.50-BL-EP2.5</t>
-  </si>
-  <si>
-    <t>24.765mm</t>
-  </si>
-  <si>
-    <t>23.515mm</t>
-  </si>
-  <si>
-    <t>-15.658mm</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>LR8341A-T33</t>
-  </si>
-  <si>
-    <t>SOT-23-3L_L2.9-W1.6-P1.90-LS2.8-BL</t>
-  </si>
-  <si>
-    <t>28.133mm</t>
-  </si>
-  <si>
-    <t>-19.299mm</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>40.259mm</t>
-  </si>
-  <si>
-    <t>-24.511mm</t>
-  </si>
-  <si>
-    <t>41.509mm</t>
-  </si>
-  <si>
-    <t>-22.569mm</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>0805W8F0000T5E</t>
-  </si>
-  <si>
-    <t>29.464mm</t>
-  </si>
-  <si>
-    <t>-7.239mm</t>
-  </si>
-  <si>
-    <t>28.464mm</t>
-  </si>
-  <si>
-    <t>0Ω</t>
+    <t>ERS1VM221F12OT</t>
+  </si>
+  <si>
+    <t>CAP-TH_BD8.0-P3.50-D0.6-FD</t>
+  </si>
+  <si>
+    <t>17.526mm</t>
+  </si>
+  <si>
+    <t>22.86mm</t>
+  </si>
+  <si>
+    <t>19.276mm</t>
+  </si>
+  <si>
+    <t>220uF</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="20" customWidth="1"/>
@@ -1141,10 +1117,10 @@
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J2">
         <v>2</v>
@@ -1153,7 +1129,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M2" t="s">
         <v>22</v>
@@ -1200,42 +1176,42 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
         <v>30</v>
       </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
       <c r="O3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
         <v>32</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
       </c>
       <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
       <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
         <v>34</v>
       </c>
-      <c r="G4" t="s">
-        <v>35</v>
-      </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I4" t="s">
         <v>35</v>
@@ -1247,45 +1223,45 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -1294,45 +1270,45 @@
         <v>21</v>
       </c>
       <c r="L5">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" t="s">
         <v>30</v>
       </c>
-      <c r="N5" t="s">
-        <v>44</v>
-      </c>
       <c r="O5" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
         <v>40</v>
       </c>
-      <c r="D6" t="s">
-        <v>47</v>
-      </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -1341,45 +1317,45 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M6" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="O6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I7" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -1388,45 +1364,45 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N7" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="O7" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I8" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -1435,45 +1411,45 @@
         <v>21</v>
       </c>
       <c r="L8">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M8" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" t="s">
         <v>30</v>
       </c>
-      <c r="N8" t="s">
-        <v>31</v>
-      </c>
       <c r="O8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -1482,21 +1458,21 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M9" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="O9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
         <v>25</v>
@@ -1505,22 +1481,22 @@
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="H10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I10" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="J10">
         <v>2</v>
@@ -1529,45 +1505,45 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" t="s">
         <v>30</v>
       </c>
-      <c r="N10" t="s">
-        <v>31</v>
-      </c>
       <c r="O10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I11" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -1576,45 +1552,45 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M11" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -1623,45 +1599,45 @@
         <v>21</v>
       </c>
       <c r="L12">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M12" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N12" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O12" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1670,45 +1646,45 @@
         <v>21</v>
       </c>
       <c r="L13">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N13" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="O13" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H14" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1717,45 +1693,45 @@
         <v>21</v>
       </c>
       <c r="L14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M14" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N14" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O14" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -1764,45 +1740,45 @@
         <v>21</v>
       </c>
       <c r="L15">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N15" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="O15" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" t="s">
         <v>79</v>
       </c>
-      <c r="B16" t="s">
+      <c r="F16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s">
         <v>80</v>
       </c>
-      <c r="C16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" t="s">
-        <v>84</v>
-      </c>
       <c r="I16" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -1814,42 +1790,42 @@
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N16" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="O16" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" t="s">
         <v>86</v>
       </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" t="s">
-        <v>89</v>
-      </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -1861,42 +1837,42 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" t="s">
         <v>90</v>
       </c>
-      <c r="B18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" t="s">
-        <v>94</v>
-      </c>
-      <c r="H18" t="s">
-        <v>95</v>
-      </c>
       <c r="I18" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -1905,45 +1881,45 @@
         <v>21</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M18" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N18" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O18" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19" t="s">
         <v>96</v>
-      </c>
-      <c r="B19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" t="s">
-        <v>100</v>
-      </c>
-      <c r="I19" t="s">
-        <v>99</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -1952,45 +1928,45 @@
         <v>21</v>
       </c>
       <c r="L19">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M19" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="N19" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="O19" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" t="s">
         <v>101</v>
-      </c>
-      <c r="B20" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" t="s">
-        <v>105</v>
-      </c>
-      <c r="H20" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" t="s">
-        <v>105</v>
       </c>
       <c r="J20">
         <v>2</v>
@@ -1999,45 +1975,45 @@
         <v>21</v>
       </c>
       <c r="L20">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M20" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="N20" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="O20" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" t="s">
         <v>103</v>
       </c>
-      <c r="D21" t="s">
-        <v>108</v>
-      </c>
       <c r="E21" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="F21" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G21" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="H21" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I21" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -2046,139 +2022,139 @@
         <v>21</v>
       </c>
       <c r="L21">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M21" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="N21" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="O21" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F22" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G22" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I22" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K22" t="s">
         <v>21</v>
       </c>
       <c r="L22">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="N22" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="O22" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" t="s">
+        <v>116</v>
+      </c>
+      <c r="H23" t="s">
         <v>117</v>
       </c>
-      <c r="B23" t="s">
+      <c r="I23" t="s">
         <v>118</v>
       </c>
-      <c r="C23" t="s">
+      <c r="J23">
+        <v>9</v>
+      </c>
+      <c r="K23" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23">
+        <v>270</v>
+      </c>
+      <c r="M23" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" t="s">
         <v>119</v>
       </c>
-      <c r="D23" t="s">
-        <v>120</v>
-      </c>
-      <c r="E23" t="s">
-        <v>121</v>
-      </c>
-      <c r="F23" t="s">
-        <v>120</v>
-      </c>
-      <c r="G23" t="s">
-        <v>121</v>
-      </c>
-      <c r="H23" t="s">
-        <v>122</v>
-      </c>
-      <c r="I23" t="s">
-        <v>123</v>
-      </c>
-      <c r="J23">
-        <v>8</v>
-      </c>
-      <c r="K23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23" t="s">
-        <v>30</v>
-      </c>
-      <c r="N23" t="s">
-        <v>118</v>
-      </c>
       <c r="O23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" t="s">
+        <v>122</v>
+      </c>
+      <c r="H24" t="s">
+        <v>123</v>
+      </c>
+      <c r="I24" t="s">
         <v>124</v>
-      </c>
-      <c r="B24" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" t="s">
-        <v>126</v>
-      </c>
-      <c r="D24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" t="s">
-        <v>128</v>
-      </c>
-      <c r="F24" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" t="s">
-        <v>128</v>
-      </c>
-      <c r="H24" t="s">
-        <v>129</v>
-      </c>
-      <c r="I24" t="s">
-        <v>130</v>
       </c>
       <c r="J24">
         <v>9</v>
@@ -2190,42 +2166,42 @@
         <v>270</v>
       </c>
       <c r="M24" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N24" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="O24" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" t="s">
         <v>126</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>127</v>
       </c>
-      <c r="E25" t="s">
-        <v>133</v>
-      </c>
       <c r="F25" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" t="s">
         <v>127</v>
       </c>
-      <c r="G25" t="s">
-        <v>133</v>
-      </c>
       <c r="H25" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" t="s">
         <v>129</v>
-      </c>
-      <c r="I25" t="s">
-        <v>134</v>
       </c>
       <c r="J25">
         <v>9</v>
@@ -2234,45 +2210,45 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N25" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="O25" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F26" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G26" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H26" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I26" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -2281,45 +2257,45 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M26" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N26" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="O26" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F27" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G27" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H27" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I27" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J27">
         <v>9</v>
@@ -2328,45 +2304,45 @@
         <v>21</v>
       </c>
       <c r="L27">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M27" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N27" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="O27" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E28" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F28" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G28" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H28" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I28" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J28">
         <v>9</v>
@@ -2378,42 +2354,42 @@
         <v>90</v>
       </c>
       <c r="M28" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N28" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="O28" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="F29" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="G29" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="H29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I29" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -2422,45 +2398,45 @@
         <v>21</v>
       </c>
       <c r="L29">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N29" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="O29" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" t="s">
+        <v>152</v>
+      </c>
+      <c r="F30" t="s">
+        <v>151</v>
+      </c>
+      <c r="G30" t="s">
+        <v>152</v>
+      </c>
+      <c r="H30" t="s">
         <v>153</v>
       </c>
-      <c r="B30" t="s">
-        <v>125</v>
-      </c>
-      <c r="C30" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="I30" t="s">
         <v>154</v>
-      </c>
-      <c r="E30" t="s">
-        <v>155</v>
-      </c>
-      <c r="F30" t="s">
-        <v>154</v>
-      </c>
-      <c r="G30" t="s">
-        <v>155</v>
-      </c>
-      <c r="H30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I30" t="s">
-        <v>157</v>
       </c>
       <c r="J30">
         <v>9</v>
@@ -2472,89 +2448,89 @@
         <v>180</v>
       </c>
       <c r="M30" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N30" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="O30" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" t="s">
         <v>158</v>
       </c>
-      <c r="B31" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" t="s">
-        <v>126</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>159</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
+        <v>158</v>
+      </c>
+      <c r="G31" t="s">
+        <v>159</v>
+      </c>
+      <c r="H31" t="s">
         <v>160</v>
       </c>
-      <c r="F31" t="s">
+      <c r="I31" t="s">
         <v>159</v>
       </c>
-      <c r="G31" t="s">
-        <v>160</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31">
+        <v>180</v>
+      </c>
+      <c r="M31" t="s">
+        <v>22</v>
+      </c>
+      <c r="N31" t="s">
         <v>161</v>
       </c>
-      <c r="I31" t="s">
-        <v>162</v>
-      </c>
-      <c r="J31">
-        <v>9</v>
-      </c>
-      <c r="K31" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31" t="s">
-        <v>30</v>
-      </c>
-      <c r="N31" t="s">
-        <v>131</v>
-      </c>
       <c r="O31" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" t="s">
         <v>163</v>
       </c>
-      <c r="B32" t="s">
+      <c r="E32" t="s">
         <v>164</v>
       </c>
-      <c r="C32" t="s">
+      <c r="F32" t="s">
+        <v>163</v>
+      </c>
+      <c r="G32" t="s">
+        <v>164</v>
+      </c>
+      <c r="H32" t="s">
         <v>165</v>
       </c>
-      <c r="D32" t="s">
-        <v>166</v>
-      </c>
-      <c r="E32" t="s">
-        <v>167</v>
-      </c>
-      <c r="F32" t="s">
-        <v>166</v>
-      </c>
-      <c r="G32" t="s">
-        <v>167</v>
-      </c>
-      <c r="H32" t="s">
-        <v>168</v>
-      </c>
       <c r="I32" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J32">
         <v>2</v>
@@ -2563,45 +2539,45 @@
         <v>21</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M32" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N32" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="O32" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C33" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E33" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F33" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G33" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H33" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="I33" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J33">
         <v>2</v>
@@ -2613,42 +2589,42 @@
         <v>180</v>
       </c>
       <c r="M33" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N33" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="O33" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E34" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F34" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="G34" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H34" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I34" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J34">
         <v>2</v>
@@ -2657,45 +2633,45 @@
         <v>21</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M34" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N34" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="O34" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C35" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D35" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F35" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H35" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I35" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="J35">
         <v>2</v>
@@ -2707,42 +2683,42 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N35" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="O35" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B36" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C36" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D36" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E36" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F36" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G36" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H36" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I36" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J36">
         <v>2</v>
@@ -2754,92 +2730,92 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N36" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="O36" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B37" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="C37" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D37" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E37" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="F37" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G37" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="H37" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I37" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" t="s">
         <v>21</v>
       </c>
       <c r="L37">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="N37" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O37" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>187</v>
+      </c>
+      <c r="B38" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" t="s">
+        <v>190</v>
+      </c>
+      <c r="E38" t="s">
         <v>191</v>
       </c>
-      <c r="B38" t="s">
+      <c r="F38" t="s">
+        <v>190</v>
+      </c>
+      <c r="G38" t="s">
+        <v>191</v>
+      </c>
+      <c r="H38" t="s">
         <v>192</v>
       </c>
-      <c r="C38" t="s">
+      <c r="I38" t="s">
         <v>193</v>
       </c>
-      <c r="D38" t="s">
-        <v>194</v>
-      </c>
-      <c r="E38" t="s">
-        <v>195</v>
-      </c>
-      <c r="F38" t="s">
-        <v>194</v>
-      </c>
-      <c r="G38" t="s">
-        <v>195</v>
-      </c>
-      <c r="H38" t="s">
-        <v>196</v>
-      </c>
-      <c r="I38" t="s">
-        <v>195</v>
-      </c>
       <c r="J38">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K38" t="s">
         <v>21</v>
@@ -2851,133 +2827,133 @@
         <v>22</v>
       </c>
       <c r="N38" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="O38" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>194</v>
+      </c>
+      <c r="B39" t="s">
+        <v>188</v>
+      </c>
+      <c r="C39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" t="s">
+        <v>196</v>
+      </c>
+      <c r="F39" t="s">
+        <v>195</v>
+      </c>
+      <c r="G39" t="s">
+        <v>196</v>
+      </c>
+      <c r="H39" t="s">
         <v>197</v>
       </c>
-      <c r="B39" t="s">
+      <c r="I39" t="s">
         <v>198</v>
       </c>
-      <c r="C39" t="s">
-        <v>199</v>
-      </c>
-      <c r="D39" t="s">
-        <v>200</v>
-      </c>
-      <c r="E39" t="s">
-        <v>201</v>
-      </c>
-      <c r="F39" t="s">
-        <v>200</v>
-      </c>
-      <c r="G39" t="s">
-        <v>201</v>
-      </c>
-      <c r="H39" t="s">
-        <v>202</v>
-      </c>
-      <c r="I39" t="s">
-        <v>203</v>
-      </c>
       <c r="J39">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K39" t="s">
         <v>21</v>
       </c>
       <c r="L39">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M39" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N39" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="O39" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>199</v>
+      </c>
+      <c r="B40" t="s">
+        <v>200</v>
+      </c>
+      <c r="C40" t="s">
+        <v>201</v>
+      </c>
+      <c r="D40" t="s">
+        <v>108</v>
+      </c>
+      <c r="E40" t="s">
+        <v>202</v>
+      </c>
+      <c r="F40" t="s">
+        <v>108</v>
+      </c>
+      <c r="G40" t="s">
+        <v>202</v>
+      </c>
+      <c r="H40" t="s">
+        <v>203</v>
+      </c>
+      <c r="I40" t="s">
         <v>204</v>
       </c>
-      <c r="B40" t="s">
-        <v>205</v>
-      </c>
-      <c r="C40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D40" t="s">
-        <v>207</v>
-      </c>
-      <c r="E40" t="s">
-        <v>180</v>
-      </c>
-      <c r="F40" t="s">
-        <v>207</v>
-      </c>
-      <c r="G40" t="s">
-        <v>180</v>
-      </c>
-      <c r="H40" t="s">
-        <v>208</v>
-      </c>
-      <c r="I40" t="s">
-        <v>209</v>
-      </c>
       <c r="J40">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K40" t="s">
         <v>21</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M40" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N40" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="O40" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" t="s">
+        <v>206</v>
+      </c>
+      <c r="C41" t="s">
+        <v>207</v>
+      </c>
+      <c r="D41" t="s">
+        <v>208</v>
+      </c>
+      <c r="E41" t="s">
+        <v>137</v>
+      </c>
+      <c r="F41" t="s">
+        <v>208</v>
+      </c>
+      <c r="G41" t="s">
+        <v>137</v>
+      </c>
+      <c r="H41" t="s">
+        <v>209</v>
+      </c>
+      <c r="I41" t="s">
         <v>210</v>
-      </c>
-      <c r="B41" t="s">
-        <v>211</v>
-      </c>
-      <c r="C41" t="s">
-        <v>212</v>
-      </c>
-      <c r="D41" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" t="s">
-        <v>66</v>
-      </c>
-      <c r="F41" t="s">
-        <v>51</v>
-      </c>
-      <c r="G41" t="s">
-        <v>66</v>
-      </c>
-      <c r="H41" t="s">
-        <v>213</v>
-      </c>
-      <c r="I41" t="s">
-        <v>214</v>
       </c>
       <c r="J41">
         <v>3</v>
@@ -2989,45 +2965,45 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N41" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="O41" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>211</v>
+      </c>
+      <c r="B42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C42" t="s">
+        <v>213</v>
+      </c>
+      <c r="D42" t="s">
+        <v>214</v>
+      </c>
+      <c r="E42" t="s">
         <v>215</v>
       </c>
-      <c r="B42" t="s">
-        <v>205</v>
-      </c>
-      <c r="C42" t="s">
-        <v>206</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
+        <v>214</v>
+      </c>
+      <c r="G42" t="s">
+        <v>215</v>
+      </c>
+      <c r="H42" t="s">
         <v>216</v>
       </c>
-      <c r="E42" t="s">
-        <v>217</v>
-      </c>
-      <c r="F42" t="s">
-        <v>216</v>
-      </c>
-      <c r="G42" t="s">
-        <v>217</v>
-      </c>
-      <c r="H42" t="s">
-        <v>218</v>
-      </c>
       <c r="I42" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="J42">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K42" t="s">
         <v>21</v>
@@ -3036,60 +3012,13 @@
         <v>180</v>
       </c>
       <c r="M42" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="N42" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="O42" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>220</v>
-      </c>
-      <c r="B43" t="s">
-        <v>221</v>
-      </c>
-      <c r="C43" t="s">
-        <v>165</v>
-      </c>
-      <c r="D43" t="s">
-        <v>222</v>
-      </c>
-      <c r="E43" t="s">
-        <v>223</v>
-      </c>
-      <c r="F43" t="s">
-        <v>222</v>
-      </c>
-      <c r="G43" t="s">
-        <v>223</v>
-      </c>
-      <c r="H43" t="s">
-        <v>224</v>
-      </c>
-      <c r="I43" t="s">
-        <v>223</v>
-      </c>
-      <c r="J43">
-        <v>2</v>
-      </c>
-      <c r="K43" t="s">
-        <v>21</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43" t="s">
-        <v>30</v>
-      </c>
-      <c r="N43" t="s">
-        <v>225</v>
-      </c>
-      <c r="O43" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
